--- a/Unified_PDF_Platform/unified_outputs/AMWINS Transamerica BLH Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/AMWINS Transamerica BLH Feb-25 Inv_invoice.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,16 +504,6 @@
           <t>ADJUSTMENT_PREMIUM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>PRICING_ADJUSTMENT</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_AMOUNT</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,7 +519,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,10 +529,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MICHELLE M</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>MICHELLE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -553,22 +547,18 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N2" t="n">
         <v>44.91</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,7 +574,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,22 +598,18 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>44.91</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,7 +625,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -649,10 +635,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>THURMAN L</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>THURMAN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -663,22 +653,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>44.91</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -694,7 +680,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -718,22 +704,18 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>FF</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
         </is>
       </c>
       <c r="N5" t="n">
         <v>136.92</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -749,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -773,22 +755,18 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N6" t="n">
         <v>44.91</v>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -804,7 +782,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -814,10 +792,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ELIZABETH A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>ELIZABETH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -828,22 +810,18 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N7" t="n">
         <v>44.91</v>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -859,7 +837,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -869,10 +847,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALISHA N</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>ALISHA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -883,22 +865,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N8" t="n">
         <v>44.91</v>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -914,7 +892,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -924,10 +902,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RYAN M</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>RYAN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -938,22 +920,18 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N9" t="n">
         <v>44.91</v>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -969,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -979,10 +957,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NATHAN J</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>NATHAN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -993,22 +975,18 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>44.91</v>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1024,7 +1002,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,22 +1026,18 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>44.91</v>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1079,7 +1053,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1103,22 +1077,18 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N12" t="n">
         <v>44.91</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1134,7 +1104,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1158,22 +1128,18 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>44.91</v>
       </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1189,7 +1155,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1213,22 +1179,18 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>44.91</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1244,7 +1206,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1268,22 +1230,18 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>44.91</v>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1299,7 +1257,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1323,22 +1281,18 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>44.91</v>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1354,7 +1308,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1378,22 +1332,18 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>EC</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>80.17</v>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1409,7 +1359,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1433,22 +1383,18 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>44.91</v>
       </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1464,7 +1410,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1488,22 +1434,18 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>44.91</v>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1519,7 +1461,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1529,10 +1471,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>STEPHANIE L</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>STEPHANIE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1543,22 +1489,18 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>MEDICAL</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N20" t="n">
         <v>44.91</v>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1574,7 +1516,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1584,28 +1526,28 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NATALIE L</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>NATALIE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N21" t="n">
         <v>44.91</v>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1621,7 +1563,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1639,20 +1581,16 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N22" t="n">
         <v>44.91</v>
       </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1668,7 +1606,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1686,20 +1624,16 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N23" t="n">
         <v>44.91</v>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1715,7 +1649,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1733,20 +1667,16 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N24" t="n">
         <v>44.91</v>
       </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1762,7 +1692,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1780,20 +1710,16 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N25" t="n">
         <v>44.91</v>
       </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1809,38 +1735,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MCCOY IV</t>
+          <t>MCCOY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WILLIAM M</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N26" t="n">
         <v>44.91</v>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1856,7 +1782,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1874,20 +1800,16 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1903,7 +1825,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1913,28 +1835,28 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JOHN W</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1950,7 +1872,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,20 +1890,16 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N29" t="n">
         <v>44.91</v>
       </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1997,7 +1915,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2015,20 +1933,16 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N30" t="n">
         <v>44.91</v>
       </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2044,7 +1958,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2054,28 +1968,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VICKI L</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>VICKI</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N31" t="n">
         <v>44.91</v>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2091,7 +2005,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2101,28 +2015,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PATRICIA A</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>PATRICIA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N32" t="n">
         <v>44.91</v>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2138,7 +2052,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2156,20 +2070,16 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N33" t="n">
         <v>44.91</v>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2185,7 +2095,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2195,28 +2105,28 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DALTON J</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>DALTON</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2232,7 +2142,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2250,20 +2160,16 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2279,7 +2185,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2289,28 +2195,28 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JAMES C</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>FF</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
       <c r="N36" t="n">
         <v>136.92</v>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2326,7 +2232,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2344,20 +2250,16 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N37" t="n">
         <v>44.91</v>
       </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2373,7 +2275,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2383,28 +2285,28 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HEATHER M</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>HEATHER</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>80.17</v>
       </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2420,7 +2322,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2437,20 +2339,22 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>TC3 CW 2000/2000 Plan (IP, OP, 2500AMB, INF, EC, ILAB)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N39" t="n">
         <v>44.91</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>2797.09</v>
+      <c r="O39" t="n">
+        <v>44.91</v>
       </c>
     </row>
     <row r="40">
@@ -2467,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2485,20 +2389,16 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N40" t="n">
         <v>44.91</v>
       </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2514,7 +2414,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2524,28 +2424,28 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ANDREA M</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>ANDREA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>44.91</v>
       </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2561,7 +2461,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2571,28 +2471,28 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BREE A</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>BREE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N42" t="n">
         <v>44.91</v>
       </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2608,7 +2508,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2618,28 +2518,28 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DAVID A</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2655,7 +2555,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2665,28 +2565,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARY SAINT</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>MARY</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SAINT</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N44" t="n">
         <v>44.91</v>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2702,7 +2602,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2720,20 +2620,16 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N45" t="n">
         <v>44.91</v>
       </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2749,7 +2645,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2759,28 +2655,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ERWIN M</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>ERWIN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N46" t="n">
         <v>44.91</v>
       </c>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2796,7 +2692,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2814,20 +2710,16 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N47" t="n">
         <v>44.91</v>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2843,7 +2735,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,20 +2753,16 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N48" t="n">
         <v>44.91</v>
       </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2890,7 +2778,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2900,28 +2788,28 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BRIAN K</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>BRIAN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>FF</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
       <c r="N49" t="n">
         <v>136.92</v>
       </c>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2937,7 +2825,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2955,20 +2843,16 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N50" t="n">
         <v>44.91</v>
       </c>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2984,7 +2868,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02/01/2025 - 02/28/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2994,10 +2878,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>STEVEN A</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>STEVEN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -3012,57 +2900,52 @@
       <c r="O51" t="n">
         <v>-44.91</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
-        <v>2797.09</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AMWINS Transamerica BLH Feb-25 Inv.pdf</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>8789335</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>02/01/2025 - 02/28/2025</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SPAIN</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>NETRECIA</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>TC3 CW 2000/2000 Plan (IP, OP, 2500AMB, INF, EC, ILAB)</t>
+          <t>TOTAL CURRENT PREMIUM</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
+      <c r="N52" t="n">
         <v>2797.09</v>
       </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (COMBINED)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>2797.09</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
